--- a/02_DIA_inicio_2026_analisis_assets/rbd_9706_escuela-bas-oscar-encalada-yovanovich_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9706_escuela-bas-oscar-encalada-yovanovich_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{831F3FDA-C6B2-4FC5-A757-0FD7D1D243A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{555BE1D5-1E1E-4A18-8E50-F7291CD2A69C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C84CC52-C9A8-4D28-A4A2-61FF61FF4825}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F01D2269-4B65-4D0B-8767-A2665A3447FE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C5B2D5E-B533-4441-B8B8-CF4485E4EB52}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFBCCA89-5922-433F-8E63-123B1224EEF8}"/>
 </file>